--- a/data/trans_orig/IP29B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses con lactancia materna exclusiva</t>
+          <t>Meses con lactancia materna exclusiva (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,6</t>
+          <t>6,48; 11,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,01</t>
+          <t>6,33; 11,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,41</t>
+          <t>6,78; 10,44</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,33</t>
+          <t>6,47; 9,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,42</t>
+          <t>7,49; 10,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 9,33</t>
+          <t>7,27; 9,4</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 12,31</t>
+          <t>9,18; 12,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,42</t>
+          <t>7,22; 9,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,32</t>
+          <t>8,4; 10,32</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,86</t>
+          <t>7,06; 9,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 10,39</t>
+          <t>7,7; 10,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,6</t>
+          <t>7,76; 9,8</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 9,63</t>
+          <t>8,0; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,47</t>
+          <t>7,99; 9,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,31</t>
+          <t>8,22; 9,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Edad-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,47</t>
+          <t>6,32; 11,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,2</t>
+          <t>6,24; 11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,44</t>
+          <t>6,98; 10,49</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,52</t>
+          <t>6,32; 9,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,42</t>
+          <t>7,4; 10,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,4</t>
+          <t>7,19; 9,24</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,43</t>
+          <t>9,16; 12,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,5</t>
+          <t>7,18; 9,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,32</t>
+          <t>8,36; 10,31</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,56</t>
+          <t>7,08; 9,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,55</t>
+          <t>7,78; 10,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 9,8</t>
+          <t>7,73; 9,59</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 9,6</t>
+          <t>7,99; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,5</t>
+          <t>8,02; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 9,32</t>
+          <t>8,17; 9,32</t>
         </is>
       </c>
     </row>
